--- a/Assets/Ressources/Stats/Boats_stats.xlsx
+++ b/Assets/Ressources/Stats/Boats_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Ressources\Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D6BC30-9A41-4DF6-BCDC-F00259E7F4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137FDE43-63C2-4913-A1BD-21609A9242EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Speed</t>
   </si>
@@ -60,6 +60,15 @@
   </si>
   <si>
     <t>Level</t>
+  </si>
+  <si>
+    <t>Coins</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>Steal</t>
   </si>
 </sst>
 </file>
@@ -377,10 +386,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -405,8 +414,17 @@
       <c r="H1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -431,3342 +449,3351 @@
       <c r="H2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
-        <f>A2+1</f>
+        <f t="shared" ref="A3:A34" si="0">A2+1</f>
         <v>2</v>
       </c>
       <c r="B3">
-        <f>INT(B$2 + ($A3 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B3:H12" si="1">INT(B$2 + ($A3 - 1) * ((B$101 - B$2) / 99))</f>
         <v>1</v>
       </c>
       <c r="C3">
-        <f>INT(C$2 + ($A3 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>3010</v>
       </c>
       <c r="D3">
-        <f>INT(D$2 + ($A3 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>505</v>
       </c>
       <c r="E3">
-        <f>INT(E$2 + ($A3 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>453</v>
       </c>
       <c r="F3">
-        <f>INT(F$2 + ($A3 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G3">
-        <f>INT(G$2 + ($A3 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H3">
-        <f>INT(H$2 + ($A3 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
-        <f>A3+1</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4">
-        <f>INT(B$2 + ($A4 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C4">
-        <f>INT(C$2 + ($A4 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>5020</v>
       </c>
       <c r="D4">
-        <f>INT(D$2 + ($A4 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1010</v>
       </c>
       <c r="E4">
-        <f>INT(E$2 + ($A4 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>857</v>
       </c>
       <c r="F4">
-        <f>INT(F$2 + ($A4 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G4">
-        <f>INT(G$2 + ($A4 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H4">
-        <f>INT(H$2 + ($A4 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
-        <f>A4+1</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5">
-        <f>INT(B$2 + ($A5 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C5">
-        <f>INT(C$2 + ($A5 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>7030</v>
       </c>
       <c r="D5">
-        <f>INT(D$2 + ($A5 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1515</v>
       </c>
       <c r="E5">
-        <f>INT(E$2 + ($A5 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1260</v>
       </c>
       <c r="F5">
-        <f>INT(F$2 + ($A5 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G5">
-        <f>INT(G$2 + ($A5 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H5">
-        <f>INT(H$2 + ($A5 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
-        <f>A5+1</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6">
-        <f>INT(B$2 + ($A6 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C6">
-        <f>INT(C$2 + ($A6 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>9040</v>
       </c>
       <c r="D6">
-        <f>INT(D$2 + ($A6 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2020</v>
       </c>
       <c r="E6">
-        <f>INT(E$2 + ($A6 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1664</v>
       </c>
       <c r="F6">
-        <f>INT(F$2 + ($A6 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G6">
-        <f>INT(G$2 + ($A6 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H6">
-        <f>INT(H$2 + ($A6 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
-        <f>A6+1</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7">
-        <f>INT(B$2 + ($A7 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C7">
-        <f>INT(C$2 + ($A7 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>11050</v>
       </c>
       <c r="D7">
-        <f>INT(D$2 + ($A7 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2525</v>
       </c>
       <c r="E7">
-        <f>INT(E$2 + ($A7 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2067</v>
       </c>
       <c r="F7">
-        <f>INT(F$2 + ($A7 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G7">
-        <f>INT(G$2 + ($A7 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H7">
-        <f>INT(H$2 + ($A7 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
-        <f>A7+1</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8">
-        <f>INT(B$2 + ($A8 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C8">
-        <f>INT(C$2 + ($A8 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>13060</v>
       </c>
       <c r="D8">
-        <f>INT(D$2 + ($A8 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>3030</v>
       </c>
       <c r="E8">
-        <f>INT(E$2 + ($A8 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2471</v>
       </c>
       <c r="F8">
-        <f>INT(F$2 + ($A8 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G8">
-        <f>INT(G$2 + ($A8 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="H8">
-        <f>INT(H$2 + ($A8 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
-        <f>A8+1</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9">
-        <f>INT(B$2 + ($A9 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C9">
-        <f>INT(C$2 + ($A9 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>15070</v>
       </c>
       <c r="D9">
-        <f>INT(D$2 + ($A9 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>3535</v>
       </c>
       <c r="E9">
-        <f>INT(E$2 + ($A9 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2874</v>
       </c>
       <c r="F9">
-        <f>INT(F$2 + ($A9 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G9">
-        <f>INT(G$2 + ($A9 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="H9">
-        <f>INT(H$2 + ($A9 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
-        <f>A9+1</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10">
-        <f>INT(B$2 + ($A10 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C10">
-        <f>INT(C$2 + ($A10 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>17080</v>
       </c>
       <c r="D10">
-        <f>INT(D$2 + ($A10 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>4040</v>
       </c>
       <c r="E10">
-        <f>INT(E$2 + ($A10 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>3278</v>
       </c>
       <c r="F10">
-        <f>INT(F$2 + ($A10 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G10">
-        <f>INT(G$2 + ($A10 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="H10">
-        <f>INT(H$2 + ($A10 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
-        <f>A10+1</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11">
-        <f>INT(B$2 + ($A11 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C11">
-        <f>INT(C$2 + ($A11 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>19090</v>
       </c>
       <c r="D11">
-        <f>INT(D$2 + ($A11 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>4545</v>
       </c>
       <c r="E11">
-        <f>INT(E$2 + ($A11 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>3681</v>
       </c>
       <c r="F11">
-        <f>INT(F$2 + ($A11 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G11">
-        <f>INT(G$2 + ($A11 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="H11">
-        <f>INT(H$2 + ($A11 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
-        <f>A11+1</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12">
-        <f>INT(B$2 + ($A12 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C12">
-        <f>INT(C$2 + ($A12 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>21101</v>
       </c>
       <c r="D12">
-        <f>INT(D$2 + ($A12 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>5050</v>
       </c>
       <c r="E12">
-        <f>INT(E$2 + ($A12 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>4085</v>
       </c>
       <c r="F12">
-        <f>INT(F$2 + ($A12 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G12">
-        <f>INT(G$2 + ($A12 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="H12">
-        <f>INT(H$2 + ($A12 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
-        <f>A12+1</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13">
-        <f>INT(B$2 + ($A13 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B13:H22" si="2">INT(B$2 + ($A13 - 1) * ((B$101 - B$2) / 99))</f>
         <v>1</v>
       </c>
       <c r="C13">
-        <f>INT(C$2 + ($A13 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>23111</v>
       </c>
       <c r="D13">
-        <f>INT(D$2 + ($A13 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>5555</v>
       </c>
       <c r="E13">
-        <f>INT(E$2 + ($A13 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>4488</v>
       </c>
       <c r="F13">
-        <f>INT(F$2 + ($A13 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G13">
-        <f>INT(G$2 + ($A13 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="H13">
-        <f>INT(H$2 + ($A13 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
-        <f>A13+1</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14">
-        <f>INT(B$2 + ($A14 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C14">
-        <f>INT(C$2 + ($A14 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>25121</v>
       </c>
       <c r="D14">
-        <f>INT(D$2 + ($A14 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>6060</v>
       </c>
       <c r="E14">
-        <f>INT(E$2 + ($A14 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>4892</v>
       </c>
       <c r="F14">
-        <f>INT(F$2 + ($A14 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G14">
-        <f>INT(G$2 + ($A14 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="H14">
-        <f>INT(H$2 + ($A14 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
-        <f>A14+1</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15">
-        <f>INT(B$2 + ($A15 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C15">
-        <f>INT(C$2 + ($A15 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>27131</v>
       </c>
       <c r="D15">
-        <f>INT(D$2 + ($A15 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>6565</v>
       </c>
       <c r="E15">
-        <f>INT(E$2 + ($A15 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>5295</v>
       </c>
       <c r="F15">
-        <f>INT(F$2 + ($A15 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G15">
-        <f>INT(G$2 + ($A15 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="H15">
-        <f>INT(H$2 + ($A15 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
-        <f>A15+1</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16">
-        <f>INT(B$2 + ($A16 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C16">
-        <f>INT(C$2 + ($A16 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>29141</v>
       </c>
       <c r="D16">
-        <f>INT(D$2 + ($A16 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>7070</v>
       </c>
       <c r="E16">
-        <f>INT(E$2 + ($A16 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>5699</v>
       </c>
       <c r="F16">
-        <f>INT(F$2 + ($A16 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G16">
-        <f>INT(G$2 + ($A16 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="H16">
-        <f>INT(H$2 + ($A16 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
-        <f>A16+1</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17">
-        <f>INT(B$2 + ($A17 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C17">
-        <f>INT(C$2 + ($A17 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>31151</v>
       </c>
       <c r="D17">
-        <f>INT(D$2 + ($A17 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>7575</v>
       </c>
       <c r="E17">
-        <f>INT(E$2 + ($A17 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>6103</v>
       </c>
       <c r="F17">
-        <f>INT(F$2 + ($A17 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G17">
-        <f>INT(G$2 + ($A17 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="H17">
-        <f>INT(H$2 + ($A17 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
-        <f>A17+1</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18">
-        <f>INT(B$2 + ($A18 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C18">
-        <f>INT(C$2 + ($A18 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>33161</v>
       </c>
       <c r="D18">
-        <f>INT(D$2 + ($A18 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>8080</v>
       </c>
       <c r="E18">
-        <f>INT(E$2 + ($A18 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>6506</v>
       </c>
       <c r="F18">
-        <f>INT(F$2 + ($A18 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="G18">
-        <f>INT(G$2 + ($A18 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="H18">
-        <f>INT(H$2 + ($A18 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
-        <f>A18+1</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19">
-        <f>INT(B$2 + ($A19 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C19">
-        <f>INT(C$2 + ($A19 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>35171</v>
       </c>
       <c r="D19">
-        <f>INT(D$2 + ($A19 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>8585</v>
       </c>
       <c r="E19">
-        <f>INT(E$2 + ($A19 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>6910</v>
       </c>
       <c r="F19">
-        <f>INT(F$2 + ($A19 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="G19">
-        <f>INT(G$2 + ($A19 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="H19">
-        <f>INT(H$2 + ($A19 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
-        <f>A19+1</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20">
-        <f>INT(B$2 + ($A20 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C20">
-        <f>INT(C$2 + ($A20 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>37181</v>
       </c>
       <c r="D20">
-        <f>INT(D$2 + ($A20 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>9090</v>
       </c>
       <c r="E20">
-        <f>INT(E$2 + ($A20 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>7313</v>
       </c>
       <c r="F20">
-        <f>INT(F$2 + ($A20 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="G20">
-        <f>INT(G$2 + ($A20 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="H20">
-        <f>INT(H$2 + ($A20 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
-        <f>A20+1</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21">
-        <f>INT(B$2 + ($A21 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C21">
-        <f>INT(C$2 + ($A21 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>39191</v>
       </c>
       <c r="D21">
-        <f>INT(D$2 + ($A21 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>9595</v>
       </c>
       <c r="E21">
-        <f>INT(E$2 + ($A21 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>7717</v>
       </c>
       <c r="F21">
-        <f>INT(F$2 + ($A21 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="G21">
-        <f>INT(G$2 + ($A21 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="H21">
-        <f>INT(H$2 + ($A21 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
-        <f>A21+1</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22">
-        <f>INT(B$2 + ($A22 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C22">
-        <f>INT(C$2 + ($A22 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>41202</v>
       </c>
       <c r="D22">
-        <f>INT(D$2 + ($A22 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>10101</v>
       </c>
       <c r="E22">
-        <f>INT(E$2 + ($A22 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>8120</v>
       </c>
       <c r="F22">
-        <f>INT(F$2 + ($A22 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="G22">
-        <f>INT(G$2 + ($A22 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="H22">
-        <f>INT(H$2 + ($A22 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
-        <f>A22+1</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23">
-        <f>INT(B$2 + ($A23 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B23:H32" si="3">INT(B$2 + ($A23 - 1) * ((B$101 - B$2) / 99))</f>
         <v>1</v>
       </c>
       <c r="C23">
-        <f>INT(C$2 + ($A23 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>43212</v>
       </c>
       <c r="D23">
-        <f>INT(D$2 + ($A23 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>10606</v>
       </c>
       <c r="E23">
-        <f>INT(E$2 + ($A23 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>8524</v>
       </c>
       <c r="F23">
-        <f>INT(F$2 + ($A23 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="G23">
-        <f>INT(G$2 + ($A23 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="H23">
-        <f>INT(H$2 + ($A23 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
-        <f>A23+1</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24">
-        <f>INT(B$2 + ($A24 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="C24">
-        <f>INT(C$2 + ($A24 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>45222</v>
       </c>
       <c r="D24">
-        <f>INT(D$2 + ($A24 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>11111</v>
       </c>
       <c r="E24">
-        <f>INT(E$2 + ($A24 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>8927</v>
       </c>
       <c r="F24">
-        <f>INT(F$2 + ($A24 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="G24">
-        <f>INT(G$2 + ($A24 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="H24">
-        <f>INT(H$2 + ($A24 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
-        <f>A24+1</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25">
-        <f>INT(B$2 + ($A25 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="C25">
-        <f>INT(C$2 + ($A25 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>47232</v>
       </c>
       <c r="D25">
-        <f>INT(D$2 + ($A25 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>11616</v>
       </c>
       <c r="E25">
-        <f>INT(E$2 + ($A25 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>9331</v>
       </c>
       <c r="F25">
-        <f>INT(F$2 + ($A25 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="G25">
-        <f>INT(G$2 + ($A25 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="H25">
-        <f>INT(H$2 + ($A25 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
-        <f>A25+1</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26">
-        <f>INT(B$2 + ($A26 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="C26">
-        <f>INT(C$2 + ($A26 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>49242</v>
       </c>
       <c r="D26">
-        <f>INT(D$2 + ($A26 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>12121</v>
       </c>
       <c r="E26">
-        <f>INT(E$2 + ($A26 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>9734</v>
       </c>
       <c r="F26">
-        <f>INT(F$2 + ($A26 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="G26">
-        <f>INT(G$2 + ($A26 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="H26">
-        <f>INT(H$2 + ($A26 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
-        <f>A26+1</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27">
-        <f>INT(B$2 + ($A27 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="C27">
-        <f>INT(C$2 + ($A27 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>51252</v>
       </c>
       <c r="D27">
-        <f>INT(D$2 + ($A27 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>12626</v>
       </c>
       <c r="E27">
-        <f>INT(E$2 + ($A27 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>10138</v>
       </c>
       <c r="F27">
-        <f>INT(F$2 + ($A27 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="G27">
-        <f>INT(G$2 + ($A27 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="H27">
-        <f>INT(H$2 + ($A27 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
-        <f>A27+1</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28">
-        <f>INT(B$2 + ($A28 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="C28">
-        <f>INT(C$2 + ($A28 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>53262</v>
       </c>
       <c r="D28">
-        <f>INT(D$2 + ($A28 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>13131</v>
       </c>
       <c r="E28">
-        <f>INT(E$2 + ($A28 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>10541</v>
       </c>
       <c r="F28">
-        <f>INT(F$2 + ($A28 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="G28">
-        <f>INT(G$2 + ($A28 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="H28">
-        <f>INT(H$2 + ($A28 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
-        <f>A28+1</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29">
-        <f>INT(B$2 + ($A29 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="C29">
-        <f>INT(C$2 + ($A29 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>55272</v>
       </c>
       <c r="D29">
-        <f>INT(D$2 + ($A29 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>13636</v>
       </c>
       <c r="E29">
-        <f>INT(E$2 + ($A29 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>10945</v>
       </c>
       <c r="F29">
-        <f>INT(F$2 + ($A29 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="G29">
-        <f>INT(G$2 + ($A29 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="H29">
-        <f>INT(H$2 + ($A29 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
-        <f>A29+1</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30">
-        <f>INT(B$2 + ($A30 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="C30">
-        <f>INT(C$2 + ($A30 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>57282</v>
       </c>
       <c r="D30">
-        <f>INT(D$2 + ($A30 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>14141</v>
       </c>
       <c r="E30">
-        <f>INT(E$2 + ($A30 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>11348</v>
       </c>
       <c r="F30">
-        <f>INT(F$2 + ($A30 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="G30">
-        <f>INT(G$2 + ($A30 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="H30">
-        <f>INT(H$2 + ($A30 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
-        <f>A30+1</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31">
-        <f>INT(B$2 + ($A31 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="C31">
-        <f>INT(C$2 + ($A31 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>59292</v>
       </c>
       <c r="D31">
-        <f>INT(D$2 + ($A31 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>14646</v>
       </c>
       <c r="E31">
-        <f>INT(E$2 + ($A31 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>11752</v>
       </c>
       <c r="F31">
-        <f>INT(F$2 + ($A31 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="G31">
-        <f>INT(G$2 + ($A31 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="H31">
-        <f>INT(H$2 + ($A31 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
-        <f>A31+1</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32">
-        <f>INT(B$2 + ($A32 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="C32">
-        <f>INT(C$2 + ($A32 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>61303</v>
       </c>
       <c r="D32">
-        <f>INT(D$2 + ($A32 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>15151</v>
       </c>
       <c r="E32">
-        <f>INT(E$2 + ($A32 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>12156</v>
       </c>
       <c r="F32">
-        <f>INT(F$2 + ($A32 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="G32">
-        <f>INT(G$2 + ($A32 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="H32">
-        <f>INT(H$2 + ($A32 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
-        <f>A32+1</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33">
-        <f>INT(B$2 + ($A33 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B33:H42" si="4">INT(B$2 + ($A33 - 1) * ((B$101 - B$2) / 99))</f>
         <v>2</v>
       </c>
       <c r="C33">
-        <f>INT(C$2 + ($A33 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>63313</v>
       </c>
       <c r="D33">
-        <f>INT(D$2 + ($A33 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>15656</v>
       </c>
       <c r="E33">
-        <f>INT(E$2 + ($A33 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>12559</v>
       </c>
       <c r="F33">
-        <f>INT(F$2 + ($A33 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="G33">
-        <f>INT(G$2 + ($A33 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="H33">
-        <f>INT(H$2 + ($A33 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
-        <f>A33+1</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34">
-        <f>INT(B$2 + ($A34 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="C34">
-        <f>INT(C$2 + ($A34 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>65323</v>
       </c>
       <c r="D34">
-        <f>INT(D$2 + ($A34 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>16161</v>
       </c>
       <c r="E34">
-        <f>INT(E$2 + ($A34 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>12963</v>
       </c>
       <c r="F34">
-        <f>INT(F$2 + ($A34 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="G34">
-        <f>INT(G$2 + ($A34 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="H34">
-        <f>INT(H$2 + ($A34 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
-        <f>A34+1</f>
+        <f t="shared" ref="A35:A66" si="5">A34+1</f>
         <v>34</v>
       </c>
       <c r="B35">
-        <f>INT(B$2 + ($A35 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="C35">
-        <f>INT(C$2 + ($A35 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>67333</v>
       </c>
       <c r="D35">
-        <f>INT(D$2 + ($A35 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>16666</v>
       </c>
       <c r="E35">
-        <f>INT(E$2 + ($A35 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>13366</v>
       </c>
       <c r="F35">
-        <f>INT(F$2 + ($A35 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="G35">
-        <f>INT(G$2 + ($A35 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="H35">
-        <f>INT(H$2 + ($A35 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
-        <f>A35+1</f>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="B36">
-        <f>INT(B$2 + ($A36 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="C36">
-        <f>INT(C$2 + ($A36 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>69343</v>
       </c>
       <c r="D36">
-        <f>INT(D$2 + ($A36 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>17171</v>
       </c>
       <c r="E36">
-        <f>INT(E$2 + ($A36 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>13770</v>
       </c>
       <c r="F36">
-        <f>INT(F$2 + ($A36 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="G36">
-        <f>INT(G$2 + ($A36 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="H36">
-        <f>INT(H$2 + ($A36 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
-        <f>A36+1</f>
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
       <c r="B37">
-        <f>INT(B$2 + ($A37 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="C37">
-        <f>INT(C$2 + ($A37 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>71353</v>
       </c>
       <c r="D37">
-        <f>INT(D$2 + ($A37 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>17676</v>
       </c>
       <c r="E37">
-        <f>INT(E$2 + ($A37 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>14173</v>
       </c>
       <c r="F37">
-        <f>INT(F$2 + ($A37 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="G37">
-        <f>INT(G$2 + ($A37 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="H37">
-        <f>INT(H$2 + ($A37 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
-        <f>A37+1</f>
+        <f t="shared" si="5"/>
         <v>37</v>
       </c>
       <c r="B38">
-        <f>INT(B$2 + ($A38 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="C38">
-        <f>INT(C$2 + ($A38 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>73363</v>
       </c>
       <c r="D38">
-        <f>INT(D$2 + ($A38 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>18181</v>
       </c>
       <c r="E38">
-        <f>INT(E$2 + ($A38 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>14577</v>
       </c>
       <c r="F38">
-        <f>INT(F$2 + ($A38 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G38">
-        <f>INT(G$2 + ($A38 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="H38">
-        <f>INT(H$2 + ($A38 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
-        <f>A38+1</f>
+        <f t="shared" si="5"/>
         <v>38</v>
       </c>
       <c r="B39">
-        <f>INT(B$2 + ($A39 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="C39">
-        <f>INT(C$2 + ($A39 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>75373</v>
       </c>
       <c r="D39">
-        <f>INT(D$2 + ($A39 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>18686</v>
       </c>
       <c r="E39">
-        <f>INT(E$2 + ($A39 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>14980</v>
       </c>
       <c r="F39">
-        <f>INT(F$2 + ($A39 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G39">
-        <f>INT(G$2 + ($A39 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="H39">
-        <f>INT(H$2 + ($A39 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
-        <f>A39+1</f>
+        <f t="shared" si="5"/>
         <v>39</v>
       </c>
       <c r="B40">
-        <f>INT(B$2 + ($A40 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="C40">
-        <f>INT(C$2 + ($A40 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>77383</v>
       </c>
       <c r="D40">
-        <f>INT(D$2 + ($A40 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>19191</v>
       </c>
       <c r="E40">
-        <f>INT(E$2 + ($A40 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>15384</v>
       </c>
       <c r="F40">
-        <f>INT(F$2 + ($A40 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G40">
-        <f>INT(G$2 + ($A40 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="H40">
-        <f>INT(H$2 + ($A40 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
-        <f>A40+1</f>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="B41">
-        <f>INT(B$2 + ($A41 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="C41">
-        <f>INT(C$2 + ($A41 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>79393</v>
       </c>
       <c r="D41">
-        <f>INT(D$2 + ($A41 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>19696</v>
       </c>
       <c r="E41">
-        <f>INT(E$2 + ($A41 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>15787</v>
       </c>
       <c r="F41">
-        <f>INT(F$2 + ($A41 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="G41">
-        <f>INT(G$2 + ($A41 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="H41">
-        <f>INT(H$2 + ($A41 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
-        <f>A41+1</f>
+        <f t="shared" si="5"/>
         <v>41</v>
       </c>
       <c r="B42">
-        <f>INT(B$2 + ($A42 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="C42">
-        <f>INT(C$2 + ($A42 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>81404</v>
       </c>
       <c r="D42">
-        <f>INT(D$2 + ($A42 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>20202</v>
       </c>
       <c r="E42">
-        <f>INT(E$2 + ($A42 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>16191</v>
       </c>
       <c r="F42">
-        <f>INT(F$2 + ($A42 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="G42">
-        <f>INT(G$2 + ($A42 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="H42">
-        <f>INT(H$2 + ($A42 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
-        <f>A42+1</f>
+        <f t="shared" si="5"/>
         <v>42</v>
       </c>
       <c r="B43">
-        <f>INT(B$2 + ($A43 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B43:H52" si="6">INT(B$2 + ($A43 - 1) * ((B$101 - B$2) / 99))</f>
         <v>2</v>
       </c>
       <c r="C43">
-        <f>INT(C$2 + ($A43 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>83414</v>
       </c>
       <c r="D43">
-        <f>INT(D$2 + ($A43 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>20707</v>
       </c>
       <c r="E43">
-        <f>INT(E$2 + ($A43 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>16594</v>
       </c>
       <c r="F43">
-        <f>INT(F$2 + ($A43 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="G43">
-        <f>INT(G$2 + ($A43 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="H43">
-        <f>INT(H$2 + ($A43 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
-        <f>A43+1</f>
+        <f t="shared" si="5"/>
         <v>43</v>
       </c>
       <c r="B44">
-        <f>INT(B$2 + ($A44 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="C44">
-        <f>INT(C$2 + ($A44 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>85424</v>
       </c>
       <c r="D44">
-        <f>INT(D$2 + ($A44 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>21212</v>
       </c>
       <c r="E44">
-        <f>INT(E$2 + ($A44 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>16998</v>
       </c>
       <c r="F44">
-        <f>INT(F$2 + ($A44 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="G44">
-        <f>INT(G$2 + ($A44 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="H44">
-        <f>INT(H$2 + ($A44 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
-        <f>A44+1</f>
+        <f t="shared" si="5"/>
         <v>44</v>
       </c>
       <c r="B45">
-        <f>INT(B$2 + ($A45 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="C45">
-        <f>INT(C$2 + ($A45 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>87434</v>
       </c>
       <c r="D45">
-        <f>INT(D$2 + ($A45 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>21717</v>
       </c>
       <c r="E45">
-        <f>INT(E$2 + ($A45 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>17402</v>
       </c>
       <c r="F45">
-        <f>INT(F$2 + ($A45 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="G45">
-        <f>INT(G$2 + ($A45 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="H45">
-        <f>INT(H$2 + ($A45 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
-        <f>A45+1</f>
+        <f t="shared" si="5"/>
         <v>45</v>
       </c>
       <c r="B46">
-        <f>INT(B$2 + ($A46 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="C46">
-        <f>INT(C$2 + ($A46 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>89444</v>
       </c>
       <c r="D46">
-        <f>INT(D$2 + ($A46 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>22222</v>
       </c>
       <c r="E46">
-        <f>INT(E$2 + ($A46 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>17805</v>
       </c>
       <c r="F46">
-        <f>INT(F$2 + ($A46 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="G46">
-        <f>INT(G$2 + ($A46 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="H46">
-        <f>INT(H$2 + ($A46 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
-        <f>A46+1</f>
+        <f t="shared" si="5"/>
         <v>46</v>
       </c>
       <c r="B47">
-        <f>INT(B$2 + ($A47 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="C47">
-        <f>INT(C$2 + ($A47 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>91454</v>
       </c>
       <c r="D47">
-        <f>INT(D$2 + ($A47 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>22727</v>
       </c>
       <c r="E47">
-        <f>INT(E$2 + ($A47 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>18209</v>
       </c>
       <c r="F47">
-        <f>INT(F$2 + ($A47 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="G47">
-        <f>INT(G$2 + ($A47 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="H47">
-        <f>INT(H$2 + ($A47 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
-        <f>A47+1</f>
+        <f t="shared" si="5"/>
         <v>47</v>
       </c>
       <c r="B48">
-        <f>INT(B$2 + ($A48 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="C48">
-        <f>INT(C$2 + ($A48 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>93464</v>
       </c>
       <c r="D48">
-        <f>INT(D$2 + ($A48 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>23232</v>
       </c>
       <c r="E48">
-        <f>INT(E$2 + ($A48 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>18612</v>
       </c>
       <c r="F48">
-        <f>INT(F$2 + ($A48 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="G48">
-        <f>INT(G$2 + ($A48 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="H48">
-        <f>INT(H$2 + ($A48 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
-        <f>A48+1</f>
+        <f t="shared" si="5"/>
         <v>48</v>
       </c>
       <c r="B49">
-        <f>INT(B$2 + ($A49 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="C49">
-        <f>INT(C$2 + ($A49 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>95474</v>
       </c>
       <c r="D49">
-        <f>INT(D$2 + ($A49 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>23737</v>
       </c>
       <c r="E49">
-        <f>INT(E$2 + ($A49 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>19016</v>
       </c>
       <c r="F49">
-        <f>INT(F$2 + ($A49 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="G49">
-        <f>INT(G$2 + ($A49 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="H49">
-        <f>INT(H$2 + ($A49 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
-        <f>A49+1</f>
+        <f t="shared" si="5"/>
         <v>49</v>
       </c>
       <c r="B50">
-        <f>INT(B$2 + ($A50 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="C50">
-        <f>INT(C$2 + ($A50 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>97484</v>
       </c>
       <c r="D50">
-        <f>INT(D$2 + ($A50 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>24242</v>
       </c>
       <c r="E50">
-        <f>INT(E$2 + ($A50 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>19419</v>
       </c>
       <c r="F50">
-        <f>INT(F$2 + ($A50 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="G50">
-        <f>INT(G$2 + ($A50 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="H50">
-        <f>INT(H$2 + ($A50 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
-        <f>A50+1</f>
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="B51">
-        <f>INT(B$2 + ($A51 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="C51">
-        <f>INT(C$2 + ($A51 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>99494</v>
       </c>
       <c r="D51">
-        <f>INT(D$2 + ($A51 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>24747</v>
       </c>
       <c r="E51">
-        <f>INT(E$2 + ($A51 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>19823</v>
       </c>
       <c r="F51">
-        <f>INT(F$2 + ($A51 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="G51">
-        <f>INT(G$2 + ($A51 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="H51">
-        <f>INT(H$2 + ($A51 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
-        <f>A51+1</f>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="B52">
-        <f>INT(B$2 + ($A52 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="C52">
-        <f>INT(C$2 + ($A52 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>101505</v>
       </c>
       <c r="D52">
-        <f>INT(D$2 + ($A52 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>25252</v>
       </c>
       <c r="E52">
-        <f>INT(E$2 + ($A52 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>20226</v>
       </c>
       <c r="F52">
-        <f>INT(F$2 + ($A52 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="G52">
-        <f>INT(G$2 + ($A52 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>25</v>
       </c>
       <c r="H52">
-        <f>INT(H$2 + ($A52 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="6"/>
         <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
-        <f>A52+1</f>
+        <f t="shared" si="5"/>
         <v>52</v>
       </c>
       <c r="B53">
-        <f>INT(B$2 + ($A53 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B53:H62" si="7">INT(B$2 + ($A53 - 1) * ((B$101 - B$2) / 99))</f>
         <v>3</v>
       </c>
       <c r="C53">
-        <f>INT(C$2 + ($A53 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>103515</v>
       </c>
       <c r="D53">
-        <f>INT(D$2 + ($A53 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>25757</v>
       </c>
       <c r="E53">
-        <f>INT(E$2 + ($A53 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>20630</v>
       </c>
       <c r="F53">
-        <f>INT(F$2 + ($A53 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="G53">
-        <f>INT(G$2 + ($A53 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="H53">
-        <f>INT(H$2 + ($A53 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
-        <f>A53+1</f>
+        <f t="shared" si="5"/>
         <v>53</v>
       </c>
       <c r="B54">
-        <f>INT(B$2 + ($A54 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="C54">
-        <f>INT(C$2 + ($A54 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>105525</v>
       </c>
       <c r="D54">
-        <f>INT(D$2 + ($A54 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>26262</v>
       </c>
       <c r="E54">
-        <f>INT(E$2 + ($A54 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>21033</v>
       </c>
       <c r="F54">
-        <f>INT(F$2 + ($A54 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="G54">
-        <f>INT(G$2 + ($A54 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="H54">
-        <f>INT(H$2 + ($A54 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55">
-        <f>A54+1</f>
+        <f t="shared" si="5"/>
         <v>54</v>
       </c>
       <c r="B55">
-        <f>INT(B$2 + ($A55 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="C55">
-        <f>INT(C$2 + ($A55 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>107535</v>
       </c>
       <c r="D55">
-        <f>INT(D$2 + ($A55 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>26767</v>
       </c>
       <c r="E55">
-        <f>INT(E$2 + ($A55 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>21437</v>
       </c>
       <c r="F55">
-        <f>INT(F$2 + ($A55 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="G55">
-        <f>INT(G$2 + ($A55 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="H55">
-        <f>INT(H$2 + ($A55 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
-        <f>A55+1</f>
+        <f t="shared" si="5"/>
         <v>55</v>
       </c>
       <c r="B56">
-        <f>INT(B$2 + ($A56 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="C56">
-        <f>INT(C$2 + ($A56 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>109545</v>
       </c>
       <c r="D56">
-        <f>INT(D$2 + ($A56 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>27272</v>
       </c>
       <c r="E56">
-        <f>INT(E$2 + ($A56 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>21840</v>
       </c>
       <c r="F56">
-        <f>INT(F$2 + ($A56 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="G56">
-        <f>INT(G$2 + ($A56 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>27</v>
       </c>
       <c r="H56">
-        <f>INT(H$2 + ($A56 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57">
-        <f>A56+1</f>
+        <f t="shared" si="5"/>
         <v>56</v>
       </c>
       <c r="B57">
-        <f>INT(B$2 + ($A57 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="C57">
-        <f>INT(C$2 + ($A57 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>111555</v>
       </c>
       <c r="D57">
-        <f>INT(D$2 + ($A57 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>27777</v>
       </c>
       <c r="E57">
-        <f>INT(E$2 + ($A57 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>22244</v>
       </c>
       <c r="F57">
-        <f>INT(F$2 + ($A57 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="G57">
-        <f>INT(G$2 + ($A57 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>27</v>
       </c>
       <c r="H57">
-        <f>INT(H$2 + ($A57 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
-        <f>A57+1</f>
+        <f t="shared" si="5"/>
         <v>57</v>
       </c>
       <c r="B58">
-        <f>INT(B$2 + ($A58 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="C58">
-        <f>INT(C$2 + ($A58 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>113565</v>
       </c>
       <c r="D58">
-        <f>INT(D$2 + ($A58 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>28282</v>
       </c>
       <c r="E58">
-        <f>INT(E$2 + ($A58 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>22647</v>
       </c>
       <c r="F58">
-        <f>INT(F$2 + ($A58 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="G58">
-        <f>INT(G$2 + ($A58 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="H58">
-        <f>INT(H$2 + ($A58 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
-        <f>A58+1</f>
+        <f t="shared" si="5"/>
         <v>58</v>
       </c>
       <c r="B59">
-        <f>INT(B$2 + ($A59 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="C59">
-        <f>INT(C$2 + ($A59 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>115575</v>
       </c>
       <c r="D59">
-        <f>INT(D$2 + ($A59 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>28787</v>
       </c>
       <c r="E59">
-        <f>INT(E$2 + ($A59 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>23051</v>
       </c>
       <c r="F59">
-        <f>INT(F$2 + ($A59 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="G59">
-        <f>INT(G$2 + ($A59 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="H59">
-        <f>INT(H$2 + ($A59 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
-        <f>A59+1</f>
+        <f t="shared" si="5"/>
         <v>59</v>
       </c>
       <c r="B60">
-        <f>INT(B$2 + ($A60 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="C60">
-        <f>INT(C$2 + ($A60 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>117585</v>
       </c>
       <c r="D60">
-        <f>INT(D$2 + ($A60 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>29292</v>
       </c>
       <c r="E60">
-        <f>INT(E$2 + ($A60 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>23455</v>
       </c>
       <c r="F60">
-        <f>INT(F$2 + ($A60 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="G60">
-        <f>INT(G$2 + ($A60 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
       <c r="H60">
-        <f>INT(H$2 + ($A60 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61">
-        <f>A60+1</f>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="B61">
-        <f>INT(B$2 + ($A61 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="C61">
-        <f>INT(C$2 + ($A61 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>119595</v>
       </c>
       <c r="D61">
-        <f>INT(D$2 + ($A61 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>29797</v>
       </c>
       <c r="E61">
-        <f>INT(E$2 + ($A61 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>23858</v>
       </c>
       <c r="F61">
-        <f>INT(F$2 + ($A61 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="G61">
-        <f>INT(G$2 + ($A61 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
       <c r="H61">
-        <f>INT(H$2 + ($A61 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
-        <f>A61+1</f>
+        <f t="shared" si="5"/>
         <v>61</v>
       </c>
       <c r="B62">
-        <f>INT(B$2 + ($A62 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="C62">
-        <f>INT(C$2 + ($A62 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>121606</v>
       </c>
       <c r="D62">
-        <f>INT(D$2 + ($A62 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>30303</v>
       </c>
       <c r="E62">
-        <f>INT(E$2 + ($A62 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>24262</v>
       </c>
       <c r="F62">
-        <f>INT(F$2 + ($A62 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="G62">
-        <f>INT(G$2 + ($A62 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="H62">
-        <f>INT(H$2 + ($A62 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
-        <f>A62+1</f>
+        <f t="shared" si="5"/>
         <v>62</v>
       </c>
       <c r="B63">
-        <f>INT(B$2 + ($A63 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B63:H72" si="8">INT(B$2 + ($A63 - 1) * ((B$101 - B$2) / 99))</f>
         <v>3</v>
       </c>
       <c r="C63">
-        <f>INT(C$2 + ($A63 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>123616</v>
       </c>
       <c r="D63">
-        <f>INT(D$2 + ($A63 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>30808</v>
       </c>
       <c r="E63">
-        <f>INT(E$2 + ($A63 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>24665</v>
       </c>
       <c r="F63">
-        <f>INT(F$2 + ($A63 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="G63">
-        <f>INT(G$2 + ($A63 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
       <c r="H63">
-        <f>INT(H$2 + ($A63 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
-        <f>A63+1</f>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="B64">
-        <f>INT(B$2 + ($A64 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="C64">
-        <f>INT(C$2 + ($A64 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>125626</v>
       </c>
       <c r="D64">
-        <f>INT(D$2 + ($A64 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>31313</v>
       </c>
       <c r="E64">
-        <f>INT(E$2 + ($A64 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>25069</v>
       </c>
       <c r="F64">
-        <f>INT(F$2 + ($A64 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="G64">
-        <f>INT(G$2 + ($A64 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="H64">
-        <f>INT(H$2 + ($A64 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
-        <f>A64+1</f>
+        <f t="shared" si="5"/>
         <v>64</v>
       </c>
       <c r="B65">
-        <f>INT(B$2 + ($A65 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="C65">
-        <f>INT(C$2 + ($A65 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>127636</v>
       </c>
       <c r="D65">
-        <f>INT(D$2 + ($A65 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>31818</v>
       </c>
       <c r="E65">
-        <f>INT(E$2 + ($A65 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>25472</v>
       </c>
       <c r="F65">
-        <f>INT(F$2 + ($A65 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="G65">
-        <f>INT(G$2 + ($A65 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="H65">
-        <f>INT(H$2 + ($A65 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
-        <f>A65+1</f>
+        <f t="shared" si="5"/>
         <v>65</v>
       </c>
       <c r="B66">
-        <f>INT(B$2 + ($A66 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="C66">
-        <f>INT(C$2 + ($A66 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>129646</v>
       </c>
       <c r="D66">
-        <f>INT(D$2 + ($A66 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>32323</v>
       </c>
       <c r="E66">
-        <f>INT(E$2 + ($A66 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>25876</v>
       </c>
       <c r="F66">
-        <f>INT(F$2 + ($A66 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="G66">
-        <f>INT(G$2 + ($A66 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="H66">
-        <f>INT(H$2 + ($A66 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
-        <f>A66+1</f>
+        <f t="shared" ref="A67:A101" si="9">A66+1</f>
         <v>66</v>
       </c>
       <c r="B67">
-        <f>INT(B$2 + ($A67 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="C67">
-        <f>INT(C$2 + ($A67 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>131656</v>
       </c>
       <c r="D67">
-        <f>INT(D$2 + ($A67 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>32828</v>
       </c>
       <c r="E67">
-        <f>INT(E$2 + ($A67 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>26279</v>
       </c>
       <c r="F67">
-        <f>INT(F$2 + ($A67 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="G67">
-        <f>INT(G$2 + ($A67 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="H67">
-        <f>INT(H$2 + ($A67 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
-        <f>A67+1</f>
+        <f t="shared" si="9"/>
         <v>67</v>
       </c>
       <c r="B68">
-        <f>INT(B$2 + ($A68 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="C68">
-        <f>INT(C$2 + ($A68 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>133666</v>
       </c>
       <c r="D68">
-        <f>INT(D$2 + ($A68 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>33333</v>
       </c>
       <c r="E68">
-        <f>INT(E$2 + ($A68 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>26683</v>
       </c>
       <c r="F68">
-        <f>INT(F$2 + ($A68 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="G68">
-        <f>INT(G$2 + ($A68 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>33</v>
       </c>
       <c r="H68">
-        <f>INT(H$2 + ($A68 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69">
-        <f>A68+1</f>
+        <f t="shared" si="9"/>
         <v>68</v>
       </c>
       <c r="B69">
-        <f>INT(B$2 + ($A69 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="C69">
-        <f>INT(C$2 + ($A69 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>135676</v>
       </c>
       <c r="D69">
-        <f>INT(D$2 + ($A69 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>33838</v>
       </c>
       <c r="E69">
-        <f>INT(E$2 + ($A69 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>27086</v>
       </c>
       <c r="F69">
-        <f>INT(F$2 + ($A69 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="G69">
-        <f>INT(G$2 + ($A69 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>33</v>
       </c>
       <c r="H69">
-        <f>INT(H$2 + ($A69 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
-        <f>A69+1</f>
+        <f t="shared" si="9"/>
         <v>69</v>
       </c>
       <c r="B70">
-        <f>INT(B$2 + ($A70 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="C70">
-        <f>INT(C$2 + ($A70 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>137686</v>
       </c>
       <c r="D70">
-        <f>INT(D$2 + ($A70 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>34343</v>
       </c>
       <c r="E70">
-        <f>INT(E$2 + ($A70 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>27490</v>
       </c>
       <c r="F70">
-        <f>INT(F$2 + ($A70 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="G70">
-        <f>INT(G$2 + ($A70 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="H70">
-        <f>INT(H$2 + ($A70 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71">
-        <f>A70+1</f>
+        <f t="shared" si="9"/>
         <v>70</v>
       </c>
       <c r="B71">
-        <f>INT(B$2 + ($A71 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="C71">
-        <f>INT(C$2 + ($A71 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>139696</v>
       </c>
       <c r="D71">
-        <f>INT(D$2 + ($A71 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>34848</v>
       </c>
       <c r="E71">
-        <f>INT(E$2 + ($A71 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>27893</v>
       </c>
       <c r="F71">
-        <f>INT(F$2 + ($A71 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="G71">
-        <f>INT(G$2 + ($A71 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="H71">
-        <f>INT(H$2 + ($A71 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
-        <f>A71+1</f>
+        <f t="shared" si="9"/>
         <v>71</v>
       </c>
       <c r="B72">
-        <f>INT(B$2 + ($A72 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="C72">
-        <f>INT(C$2 + ($A72 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>141707</v>
       </c>
       <c r="D72">
-        <f>INT(D$2 + ($A72 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>35353</v>
       </c>
       <c r="E72">
-        <f>INT(E$2 + ($A72 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>28297</v>
       </c>
       <c r="F72">
-        <f>INT(F$2 + ($A72 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="G72">
-        <f>INT(G$2 + ($A72 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
       <c r="H72">
-        <f>INT(H$2 + ($A72 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73">
-        <f>A72+1</f>
+        <f t="shared" si="9"/>
         <v>72</v>
       </c>
       <c r="B73">
-        <f>INT(B$2 + ($A73 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B73:H82" si="10">INT(B$2 + ($A73 - 1) * ((B$101 - B$2) / 99))</f>
         <v>3</v>
       </c>
       <c r="C73">
-        <f>INT(C$2 + ($A73 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>143717</v>
       </c>
       <c r="D73">
-        <f>INT(D$2 + ($A73 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>35858</v>
       </c>
       <c r="E73">
-        <f>INT(E$2 + ($A73 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>28701</v>
       </c>
       <c r="F73">
-        <f>INT(F$2 + ($A73 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>17</v>
       </c>
       <c r="G73">
-        <f>INT(G$2 + ($A73 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>35</v>
       </c>
       <c r="H73">
-        <f>INT(H$2 + ($A73 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
-        <f>A73+1</f>
+        <f t="shared" si="9"/>
         <v>73</v>
       </c>
       <c r="B74">
-        <f>INT(B$2 + ($A74 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="C74">
-        <f>INT(C$2 + ($A74 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>145727</v>
       </c>
       <c r="D74">
-        <f>INT(D$2 + ($A74 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>36363</v>
       </c>
       <c r="E74">
-        <f>INT(E$2 + ($A74 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>29104</v>
       </c>
       <c r="F74">
-        <f>INT(F$2 + ($A74 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="G74">
-        <f>INT(G$2 + ($A74 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
       <c r="H74">
-        <f>INT(H$2 + ($A74 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75">
-        <f>A74+1</f>
+        <f t="shared" si="9"/>
         <v>74</v>
       </c>
       <c r="B75">
-        <f>INT(B$2 + ($A75 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="C75">
-        <f>INT(C$2 + ($A75 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>147737</v>
       </c>
       <c r="D75">
-        <f>INT(D$2 + ($A75 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>36868</v>
       </c>
       <c r="E75">
-        <f>INT(E$2 + ($A75 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>29508</v>
       </c>
       <c r="F75">
-        <f>INT(F$2 + ($A75 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="G75">
-        <f>INT(G$2 + ($A75 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
       <c r="H75">
-        <f>INT(H$2 + ($A75 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
-        <f>A75+1</f>
+        <f t="shared" si="9"/>
         <v>75</v>
       </c>
       <c r="B76">
-        <f>INT(B$2 + ($A76 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="C76">
-        <f>INT(C$2 + ($A76 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>149747</v>
       </c>
       <c r="D76">
-        <f>INT(D$2 + ($A76 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>37373</v>
       </c>
       <c r="E76">
-        <f>INT(E$2 + ($A76 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>29911</v>
       </c>
       <c r="F76">
-        <f>INT(F$2 + ($A76 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="G76">
-        <f>INT(G$2 + ($A76 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
       <c r="H76">
-        <f>INT(H$2 + ($A76 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77">
-        <f>A76+1</f>
+        <f t="shared" si="9"/>
         <v>76</v>
       </c>
       <c r="B77">
-        <f>INT(B$2 + ($A77 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="C77">
-        <f>INT(C$2 + ($A77 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>151757</v>
       </c>
       <c r="D77">
-        <f>INT(D$2 + ($A77 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>37878</v>
       </c>
       <c r="E77">
-        <f>INT(E$2 + ($A77 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>30315</v>
       </c>
       <c r="F77">
-        <f>INT(F$2 + ($A77 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="G77">
-        <f>INT(G$2 + ($A77 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
       <c r="H77">
-        <f>INT(H$2 + ($A77 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
-        <f>A77+1</f>
+        <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="B78">
-        <f>INT(B$2 + ($A78 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="C78">
-        <f>INT(C$2 + ($A78 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>153767</v>
       </c>
       <c r="D78">
-        <f>INT(D$2 + ($A78 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>38383</v>
       </c>
       <c r="E78">
-        <f>INT(E$2 + ($A78 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>30718</v>
       </c>
       <c r="F78">
-        <f>INT(F$2 + ($A78 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="G78">
-        <f>INT(G$2 + ($A78 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>38</v>
       </c>
       <c r="H78">
-        <f>INT(H$2 + ($A78 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79">
-        <f>A78+1</f>
+        <f t="shared" si="9"/>
         <v>78</v>
       </c>
       <c r="B79">
-        <f>INT(B$2 + ($A79 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="C79">
-        <f>INT(C$2 + ($A79 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>155777</v>
       </c>
       <c r="D79">
-        <f>INT(D$2 + ($A79 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>38888</v>
       </c>
       <c r="E79">
-        <f>INT(E$2 + ($A79 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>31122</v>
       </c>
       <c r="F79">
-        <f>INT(F$2 + ($A79 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="G79">
-        <f>INT(G$2 + ($A79 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>38</v>
       </c>
       <c r="H79">
-        <f>INT(H$2 + ($A79 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
-        <f>A79+1</f>
+        <f t="shared" si="9"/>
         <v>79</v>
       </c>
       <c r="B80">
-        <f>INT(B$2 + ($A80 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="C80">
-        <f>INT(C$2 + ($A80 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>157787</v>
       </c>
       <c r="D80">
-        <f>INT(D$2 + ($A80 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>39393</v>
       </c>
       <c r="E80">
-        <f>INT(E$2 + ($A80 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>31525</v>
       </c>
       <c r="F80">
-        <f>INT(F$2 + ($A80 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="G80">
-        <f>INT(G$2 + ($A80 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>39</v>
       </c>
       <c r="H80">
-        <f>INT(H$2 + ($A80 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>39</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81">
-        <f>A80+1</f>
+        <f t="shared" si="9"/>
         <v>80</v>
       </c>
       <c r="B81">
-        <f>INT(B$2 + ($A81 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="C81">
-        <f>INT(C$2 + ($A81 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>159797</v>
       </c>
       <c r="D81">
-        <f>INT(D$2 + ($A81 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>39898</v>
       </c>
       <c r="E81">
-        <f>INT(E$2 + ($A81 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>31929</v>
       </c>
       <c r="F81">
-        <f>INT(F$2 + ($A81 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="G81">
-        <f>INT(G$2 + ($A81 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>39</v>
       </c>
       <c r="H81">
-        <f>INT(H$2 + ($A81 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
-        <f>A81+1</f>
+        <f t="shared" si="9"/>
         <v>81</v>
       </c>
       <c r="B82">
-        <f>INT(B$2 + ($A82 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="C82">
-        <f>INT(C$2 + ($A82 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>161808</v>
       </c>
       <c r="D82">
-        <f>INT(D$2 + ($A82 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>40404</v>
       </c>
       <c r="E82">
-        <f>INT(E$2 + ($A82 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>32332</v>
       </c>
       <c r="F82">
-        <f>INT(F$2 + ($A82 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="G82">
-        <f>INT(G$2 + ($A82 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="H82">
-        <f>INT(H$2 + ($A82 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83">
-        <f>A82+1</f>
+        <f t="shared" si="9"/>
         <v>82</v>
       </c>
       <c r="B83">
-        <f>INT(B$2 + ($A83 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B83:H92" si="11">INT(B$2 + ($A83 - 1) * ((B$101 - B$2) / 99))</f>
         <v>4</v>
       </c>
       <c r="C83">
-        <f>INT(C$2 + ($A83 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>163818</v>
       </c>
       <c r="D83">
-        <f>INT(D$2 + ($A83 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>40909</v>
       </c>
       <c r="E83">
-        <f>INT(E$2 + ($A83 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>32736</v>
       </c>
       <c r="F83">
-        <f>INT(F$2 + ($A83 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="G83">
-        <f>INT(G$2 + ($A83 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="H83">
-        <f>INT(H$2 + ($A83 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
-        <f>A83+1</f>
+        <f t="shared" si="9"/>
         <v>83</v>
       </c>
       <c r="B84">
-        <f>INT(B$2 + ($A84 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="C84">
-        <f>INT(C$2 + ($A84 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>165828</v>
       </c>
       <c r="D84">
-        <f>INT(D$2 + ($A84 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>41414</v>
       </c>
       <c r="E84">
-        <f>INT(E$2 + ($A84 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>33139</v>
       </c>
       <c r="F84">
-        <f>INT(F$2 + ($A84 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="G84">
-        <f>INT(G$2 + ($A84 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
       <c r="H84">
-        <f>INT(H$2 + ($A84 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85">
-        <f>A84+1</f>
+        <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="B85">
-        <f>INT(B$2 + ($A85 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="C85">
-        <f>INT(C$2 + ($A85 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>167838</v>
       </c>
       <c r="D85">
-        <f>INT(D$2 + ($A85 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>41919</v>
       </c>
       <c r="E85">
-        <f>INT(E$2 + ($A85 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>33543</v>
       </c>
       <c r="F85">
-        <f>INT(F$2 + ($A85 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="G85">
-        <f>INT(G$2 + ($A85 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
       <c r="H85">
-        <f>INT(H$2 + ($A85 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
-        <f>A85+1</f>
+        <f t="shared" si="9"/>
         <v>85</v>
       </c>
       <c r="B86">
-        <f>INT(B$2 + ($A86 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="C86">
-        <f>INT(C$2 + ($A86 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>169848</v>
       </c>
       <c r="D86">
-        <f>INT(D$2 + ($A86 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>42424</v>
       </c>
       <c r="E86">
-        <f>INT(E$2 + ($A86 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>33946</v>
       </c>
       <c r="F86">
-        <f>INT(F$2 + ($A86 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="G86">
-        <f>INT(G$2 + ($A86 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
       <c r="H86">
-        <f>INT(H$2 + ($A86 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87">
-        <f>A86+1</f>
+        <f t="shared" si="9"/>
         <v>86</v>
       </c>
       <c r="B87">
-        <f>INT(B$2 + ($A87 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="C87">
-        <f>INT(C$2 + ($A87 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>171858</v>
       </c>
       <c r="D87">
-        <f>INT(D$2 + ($A87 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>42929</v>
       </c>
       <c r="E87">
-        <f>INT(E$2 + ($A87 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>34350</v>
       </c>
       <c r="F87">
-        <f>INT(F$2 + ($A87 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="G87">
-        <f>INT(G$2 + ($A87 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
       <c r="H87">
-        <f>INT(H$2 + ($A87 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
-        <f>A87+1</f>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="B88">
-        <f>INT(B$2 + ($A88 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="C88">
-        <f>INT(C$2 + ($A88 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>173868</v>
       </c>
       <c r="D88">
-        <f>INT(D$2 + ($A88 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>43434</v>
       </c>
       <c r="E88">
-        <f>INT(E$2 + ($A88 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>34754</v>
       </c>
       <c r="F88">
-        <f>INT(F$2 + ($A88 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="G88">
-        <f>INT(G$2 + ($A88 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>43</v>
       </c>
       <c r="H88">
-        <f>INT(H$2 + ($A88 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>43</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89">
-        <f>A88+1</f>
+        <f t="shared" si="9"/>
         <v>88</v>
       </c>
       <c r="B89">
-        <f>INT(B$2 + ($A89 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="C89">
-        <f>INT(C$2 + ($A89 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>175878</v>
       </c>
       <c r="D89">
-        <f>INT(D$2 + ($A89 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>43939</v>
       </c>
       <c r="E89">
-        <f>INT(E$2 + ($A89 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>35157</v>
       </c>
       <c r="F89">
-        <f>INT(F$2 + ($A89 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="G89">
-        <f>INT(G$2 + ($A89 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>43</v>
       </c>
       <c r="H89">
-        <f>INT(H$2 + ($A89 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>43</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
-        <f>A89+1</f>
+        <f t="shared" si="9"/>
         <v>89</v>
       </c>
       <c r="B90">
-        <f>INT(B$2 + ($A90 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="C90">
-        <f>INT(C$2 + ($A90 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>177888</v>
       </c>
       <c r="D90">
-        <f>INT(D$2 + ($A90 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>44444</v>
       </c>
       <c r="E90">
-        <f>INT(E$2 + ($A90 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>35561</v>
       </c>
       <c r="F90">
-        <f>INT(F$2 + ($A90 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>22</v>
       </c>
       <c r="G90">
-        <f>INT(G$2 + ($A90 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>44</v>
       </c>
       <c r="H90">
-        <f>INT(H$2 + ($A90 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>44</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91">
-        <f>A90+1</f>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="B91">
-        <f>INT(B$2 + ($A91 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="C91">
-        <f>INT(C$2 + ($A91 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>179898</v>
       </c>
       <c r="D91">
-        <f>INT(D$2 + ($A91 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>44949</v>
       </c>
       <c r="E91">
-        <f>INT(E$2 + ($A91 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>35964</v>
       </c>
       <c r="F91">
-        <f>INT(F$2 + ($A91 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>22</v>
       </c>
       <c r="G91">
-        <f>INT(G$2 + ($A91 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>44</v>
       </c>
       <c r="H91">
-        <f>INT(H$2 + ($A91 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>44</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
-        <f>A91+1</f>
+        <f t="shared" si="9"/>
         <v>91</v>
       </c>
       <c r="B92">
-        <f>INT(B$2 + ($A92 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="C92">
-        <f>INT(C$2 + ($A92 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>181909</v>
       </c>
       <c r="D92">
-        <f>INT(D$2 + ($A92 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>45454</v>
       </c>
       <c r="E92">
-        <f>INT(E$2 + ($A92 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>36368</v>
       </c>
       <c r="F92">
-        <f>INT(F$2 + ($A92 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>22</v>
       </c>
       <c r="G92">
-        <f>INT(G$2 + ($A92 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>45</v>
       </c>
       <c r="H92">
-        <f>INT(H$2 + ($A92 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="11"/>
         <v>45</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93">
-        <f>A92+1</f>
+        <f t="shared" si="9"/>
         <v>92</v>
       </c>
       <c r="B93">
-        <f>INT(B$2 + ($A93 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B93:H100" si="12">INT(B$2 + ($A93 - 1) * ((B$101 - B$2) / 99))</f>
         <v>4</v>
       </c>
       <c r="C93">
-        <f>INT(C$2 + ($A93 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>183919</v>
       </c>
       <c r="D93">
-        <f>INT(D$2 + ($A93 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>45959</v>
       </c>
       <c r="E93">
-        <f>INT(E$2 + ($A93 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>36771</v>
       </c>
       <c r="F93">
-        <f>INT(F$2 + ($A93 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>22</v>
       </c>
       <c r="G93">
-        <f>INT(G$2 + ($A93 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>45</v>
       </c>
       <c r="H93">
-        <f>INT(H$2 + ($A93 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>45</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
-        <f>A93+1</f>
+        <f t="shared" si="9"/>
         <v>93</v>
       </c>
       <c r="B94">
-        <f>INT(B$2 + ($A94 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="C94">
-        <f>INT(C$2 + ($A94 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>185929</v>
       </c>
       <c r="D94">
-        <f>INT(D$2 + ($A94 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>46464</v>
       </c>
       <c r="E94">
-        <f>INT(E$2 + ($A94 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>37175</v>
       </c>
       <c r="F94">
-        <f>INT(F$2 + ($A94 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="G94">
-        <f>INT(G$2 + ($A94 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>46</v>
       </c>
       <c r="H94">
-        <f>INT(H$2 + ($A94 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>46</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95">
-        <f>A94+1</f>
+        <f t="shared" si="9"/>
         <v>94</v>
       </c>
       <c r="B95">
-        <f>INT(B$2 + ($A95 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="C95">
-        <f>INT(C$2 + ($A95 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>187939</v>
       </c>
       <c r="D95">
-        <f>INT(D$2 + ($A95 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>46969</v>
       </c>
       <c r="E95">
-        <f>INT(E$2 + ($A95 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>37578</v>
       </c>
       <c r="F95">
-        <f>INT(F$2 + ($A95 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="G95">
-        <f>INT(G$2 + ($A95 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>46</v>
       </c>
       <c r="H95">
-        <f>INT(H$2 + ($A95 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>46</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
-        <f>A95+1</f>
+        <f t="shared" si="9"/>
         <v>95</v>
       </c>
       <c r="B96">
-        <f>INT(B$2 + ($A96 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="C96">
-        <f>INT(C$2 + ($A96 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>189949</v>
       </c>
       <c r="D96">
-        <f>INT(D$2 + ($A96 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>47474</v>
       </c>
       <c r="E96">
-        <f>INT(E$2 + ($A96 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>37982</v>
       </c>
       <c r="F96">
-        <f>INT(F$2 + ($A96 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="G96">
-        <f>INT(G$2 + ($A96 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>47</v>
       </c>
       <c r="H96">
-        <f>INT(H$2 + ($A96 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97">
-        <f>A96+1</f>
+        <f t="shared" si="9"/>
         <v>96</v>
       </c>
       <c r="B97">
-        <f>INT(B$2 + ($A97 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="C97">
-        <f>INT(C$2 + ($A97 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>191959</v>
       </c>
       <c r="D97">
-        <f>INT(D$2 + ($A97 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>47979</v>
       </c>
       <c r="E97">
-        <f>INT(E$2 + ($A97 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>38385</v>
       </c>
       <c r="F97">
-        <f>INT(F$2 + ($A97 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="G97">
-        <f>INT(G$2 + ($A97 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>47</v>
       </c>
       <c r="H97">
-        <f>INT(H$2 + ($A97 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>47</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
-        <f>A97+1</f>
+        <f t="shared" si="9"/>
         <v>97</v>
       </c>
       <c r="B98">
-        <f>INT(B$2 + ($A98 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="C98">
-        <f>INT(C$2 + ($A98 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>193969</v>
       </c>
       <c r="D98">
-        <f>INT(D$2 + ($A98 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>48484</v>
       </c>
       <c r="E98">
-        <f>INT(E$2 + ($A98 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>38789</v>
       </c>
       <c r="F98">
-        <f>INT(F$2 + ($A98 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="G98">
-        <f>INT(G$2 + ($A98 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>48</v>
       </c>
       <c r="H98">
-        <f>INT(H$2 + ($A98 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>48</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99">
-        <f>A98+1</f>
+        <f t="shared" si="9"/>
         <v>98</v>
       </c>
       <c r="B99">
-        <f>INT(B$2 + ($A99 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="C99">
-        <f>INT(C$2 + ($A99 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>195979</v>
       </c>
       <c r="D99">
-        <f>INT(D$2 + ($A99 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>48989</v>
       </c>
       <c r="E99">
-        <f>INT(E$2 + ($A99 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>39192</v>
       </c>
       <c r="F99">
-        <f>INT(F$2 + ($A99 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="G99">
-        <f>INT(G$2 + ($A99 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>48</v>
       </c>
       <c r="H99">
-        <f>INT(H$2 + ($A99 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
-        <f>A99+1</f>
+        <f t="shared" si="9"/>
         <v>99</v>
       </c>
       <c r="B100">
-        <f>INT(B$2 + ($A100 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="C100">
-        <f>INT(C$2 + ($A100 - 1) * ((C$101 - C$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>197989</v>
       </c>
       <c r="D100">
-        <f>INT(D$2 + ($A100 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>49494</v>
       </c>
       <c r="E100">
-        <f>INT(E$2 + ($A100 - 1) * ((E$101 - E$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>39596</v>
       </c>
       <c r="F100">
-        <f>INT(F$2 + ($A100 - 1) * ((F$101 - F$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="G100">
-        <f>INT(G$2 + ($A100 - 1) * ((G$101 - G$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>49</v>
       </c>
       <c r="H100">
-        <f>INT(H$2 + ($A100 - 1) * ((H$101 - H$2) / 99))</f>
+        <f t="shared" si="12"/>
         <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101">
-        <f>A100+1</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="B101">

--- a/Assets/Ressources/Stats/Boats_stats.xlsx
+++ b/Assets/Ressources/Stats/Boats_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Ressources\Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F108F1A-B8C9-4DFA-9BBE-823AC1897D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF874DB-7960-4220-8D86-A5FBE5C3BB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/Ressources/Stats/Boats_stats.xlsx
+++ b/Assets/Ressources/Stats/Boats_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Ressources\Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD38701-DD7F-4882-AFAF-A3F13E898699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C894E487-D340-4ED8-99D1-8031D1428E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -489,7 +489,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -1628,17 +1628,20 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
+      <c r="K22">
+        <v>5000</v>
+      </c>
       <c r="L22">
         <v>1</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P22">
         <v>30</v>
@@ -1689,13 +1692,13 @@
         <v>1</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P23">
         <v>30</v>
@@ -1746,13 +1749,13 @@
         <v>1</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P24">
         <v>30</v>
@@ -1803,13 +1806,13 @@
         <v>1</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P25">
         <v>30</v>
@@ -1860,13 +1863,13 @@
         <v>1</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P26">
         <v>30</v>
@@ -1913,14 +1916,11 @@
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="K27">
-        <v>5000</v>
-      </c>
       <c r="L27">
         <v>1</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N27">
         <v>2</v>
@@ -1977,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="M28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28">
         <v>2</v>
@@ -2034,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="M29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N29">
         <v>2</v>
@@ -2091,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N30">
         <v>2</v>
@@ -2148,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="M31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N31">
         <v>2</v>
@@ -2205,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="M32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -2262,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="M33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33">
         <v>2</v>
@@ -2319,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="M34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N34">
         <v>2</v>
@@ -2376,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="M35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N35">
         <v>2</v>
@@ -2433,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="M36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N36">
         <v>2</v>
@@ -2490,7 +2490,7 @@
         <v>1</v>
       </c>
       <c r="M37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N37">
         <v>2</v>
@@ -2547,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="M38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N38">
         <v>2</v>
@@ -2604,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="M39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N39">
         <v>2</v>
@@ -2661,7 +2661,7 @@
         <v>1</v>
       </c>
       <c r="M40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N40">
         <v>2</v>
@@ -2718,7 +2718,7 @@
         <v>1</v>
       </c>
       <c r="M41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N41">
         <v>2</v>
@@ -2771,17 +2771,20 @@
         <f t="shared" si="5"/>
         <v>34</v>
       </c>
+      <c r="K42">
+        <v>20000</v>
+      </c>
       <c r="L42">
         <v>1</v>
       </c>
       <c r="M42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P42">
         <v>50</v>
@@ -2832,13 +2835,13 @@
         <v>1</v>
       </c>
       <c r="M43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P43">
         <v>50</v>
@@ -2889,13 +2892,13 @@
         <v>1</v>
       </c>
       <c r="M44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P44">
         <v>50</v>
@@ -2946,13 +2949,13 @@
         <v>1</v>
       </c>
       <c r="M45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P45">
         <v>50</v>
@@ -3003,13 +3006,13 @@
         <v>1</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P46">
         <v>50</v>
@@ -3060,13 +3063,13 @@
         <v>1</v>
       </c>
       <c r="M47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P47">
         <v>50</v>
@@ -3117,13 +3120,13 @@
         <v>1</v>
       </c>
       <c r="M48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P48">
         <v>50</v>
@@ -3174,13 +3177,13 @@
         <v>1</v>
       </c>
       <c r="M49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P49">
         <v>50</v>
@@ -3231,13 +3234,13 @@
         <v>1</v>
       </c>
       <c r="M50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P50">
         <v>50</v>
@@ -3288,13 +3291,13 @@
         <v>1</v>
       </c>
       <c r="M51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P51">
         <v>50</v>
@@ -3341,9 +3344,6 @@
         <f t="shared" si="9"/>
         <v>70</v>
       </c>
-      <c r="K52">
-        <v>20000</v>
-      </c>
       <c r="L52">
         <v>1</v>
       </c>
@@ -3914,17 +3914,20 @@
         <f t="shared" si="9"/>
         <v>146</v>
       </c>
+      <c r="K62">
+        <v>50000</v>
+      </c>
       <c r="L62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P62">
         <v>70</v>
@@ -3972,16 +3975,16 @@
         <v>157</v>
       </c>
       <c r="L63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P63">
         <v>70</v>
@@ -4029,16 +4032,16 @@
         <v>169</v>
       </c>
       <c r="L64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P64">
         <v>70</v>
@@ -4086,16 +4089,16 @@
         <v>182</v>
       </c>
       <c r="L65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P65">
         <v>70</v>
@@ -4143,16 +4146,16 @@
         <v>195</v>
       </c>
       <c r="L66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P66">
         <v>70</v>
@@ -4200,16 +4203,16 @@
         <v>210</v>
       </c>
       <c r="L67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P67">
         <v>70</v>
@@ -4257,16 +4260,16 @@
         <v>226</v>
       </c>
       <c r="L68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P68">
         <v>70</v>
@@ -4314,16 +4317,16 @@
         <v>243</v>
       </c>
       <c r="L69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P69">
         <v>70</v>
@@ -4371,16 +4374,16 @@
         <v>262</v>
       </c>
       <c r="L70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P70">
         <v>70</v>
@@ -4428,16 +4431,16 @@
         <v>281</v>
       </c>
       <c r="L71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P71">
         <v>70</v>
@@ -4485,16 +4488,16 @@
         <v>303</v>
       </c>
       <c r="L72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P72">
         <v>80</v>
@@ -4542,16 +4545,16 @@
         <v>325</v>
       </c>
       <c r="L73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P73">
         <v>80</v>
@@ -4599,16 +4602,16 @@
         <v>350</v>
       </c>
       <c r="L74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P74">
         <v>80</v>
@@ -4656,16 +4659,16 @@
         <v>376</v>
       </c>
       <c r="L75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P75">
         <v>80</v>
@@ -4713,16 +4716,16 @@
         <v>405</v>
       </c>
       <c r="L76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P76">
         <v>80</v>
@@ -4769,9 +4772,6 @@
         <f t="shared" si="12"/>
         <v>436</v>
       </c>
-      <c r="K77">
-        <v>75000</v>
-      </c>
       <c r="L77">
         <v>2</v>
       </c>
@@ -5000,14 +5000,17 @@
         <f t="shared" si="12"/>
         <v>583</v>
       </c>
+      <c r="K81">
+        <v>100000</v>
+      </c>
       <c r="L81">
         <v>2</v>
       </c>
       <c r="M81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O81">
         <v>5</v>
@@ -5061,10 +5064,10 @@
         <v>2</v>
       </c>
       <c r="M82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O82">
         <v>5</v>
@@ -5118,10 +5121,10 @@
         <v>2</v>
       </c>
       <c r="M83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O83">
         <v>5</v>
@@ -5175,10 +5178,10 @@
         <v>2</v>
       </c>
       <c r="M84">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N84">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O84">
         <v>5</v>
@@ -5232,10 +5235,10 @@
         <v>2</v>
       </c>
       <c r="M85">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N85">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O85">
         <v>5</v>
@@ -5289,10 +5292,10 @@
         <v>2</v>
       </c>
       <c r="M86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O86">
         <v>5</v>
@@ -5346,10 +5349,10 @@
         <v>2</v>
       </c>
       <c r="M87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O87">
         <v>5</v>
@@ -5403,10 +5406,10 @@
         <v>2</v>
       </c>
       <c r="M88">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N88">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O88">
         <v>5</v>
@@ -5460,10 +5463,10 @@
         <v>2</v>
       </c>
       <c r="M89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O89">
         <v>5</v>
@@ -5517,10 +5520,10 @@
         <v>2</v>
       </c>
       <c r="M90">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N90">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O90">
         <v>5</v>
@@ -5574,10 +5577,10 @@
         <v>2</v>
       </c>
       <c r="M91">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N91">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O91">
         <v>5</v>
@@ -5631,10 +5634,10 @@
         <v>2</v>
       </c>
       <c r="M92">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N92">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O92">
         <v>5</v>
@@ -5688,10 +5691,10 @@
         <v>2</v>
       </c>
       <c r="M93">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N93">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O93">
         <v>5</v>
@@ -5745,10 +5748,10 @@
         <v>2</v>
       </c>
       <c r="M94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O94">
         <v>5</v>
@@ -5802,10 +5805,10 @@
         <v>2</v>
       </c>
       <c r="M95">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N95">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O95">
         <v>5</v>
@@ -5859,10 +5862,10 @@
         <v>2</v>
       </c>
       <c r="M96">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N96">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O96">
         <v>5</v>
@@ -5916,10 +5919,10 @@
         <v>2</v>
       </c>
       <c r="M97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O97">
         <v>5</v>
@@ -5973,10 +5976,10 @@
         <v>2</v>
       </c>
       <c r="M98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O98">
         <v>5</v>
@@ -6030,10 +6033,10 @@
         <v>2</v>
       </c>
       <c r="M99">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N99">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O99">
         <v>5</v>
@@ -6087,10 +6090,10 @@
         <v>2</v>
       </c>
       <c r="M100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O100">
         <v>5</v>

--- a/Assets/Ressources/Stats/Boats_stats.xlsx
+++ b/Assets/Ressources/Stats/Boats_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Ressources\Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C894E487-D340-4ED8-99D1-8031D1428E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F341BCA-A053-4F0C-9436-F61FC9D9E44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Speed</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>Steal</t>
-  </si>
-  <si>
-    <t>Total</t>
   </si>
   <si>
     <t>Model cost</t>
@@ -404,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -439,22 +436,22 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
-      </c>
-      <c r="P1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -6150,23 +6147,6 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>10</v>
-      </c>
-      <c r="H102">
-        <f>SUM(H2:H101)</f>
-        <v>4546106</v>
-      </c>
-      <c r="I102">
-        <f t="shared" ref="I102:J102" si="18">SUM(I2:I101)</f>
-        <v>73345</v>
-      </c>
-      <c r="J102">
-        <f t="shared" si="18"/>
-        <v>35546</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
